--- a/Deliverables/Bracelet(Aux_v1.0)/BOM/Bracelet_Aux_v1.0.xlsx
+++ b/Deliverables/Bracelet(Aux_v1.0)/BOM/Bracelet_Aux_v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\BrianPeri-SmartWatch\Deliverables\Bracelet(Aux_v1.0)\_Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\BrianPeri-SmartWatch\Deliverables\Bracelet(Aux_v1.0)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Bracelet_Aux_v1.0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
   <si>
     <t>Description</t>
   </si>
@@ -41,9 +41,6 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0201 0.1uF 25volts X5R 10%</t>
-  </si>
-  <si>
     <t>C1, C2, C3, C4, C5</t>
   </si>
   <si>
@@ -165,17 +162,33 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 0.1UF 25V X5R 0201
+</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>Unit Cost (25 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (25)</t>
+  </si>
+  <si>
+    <t>Quantity 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,14 +224,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -295,21 +300,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -369,19 +359,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -389,21 +366,6 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -430,6 +392,179 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -440,84 +575,149 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -800,342 +1000,411 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" customWidth="1"/>
     <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="23"/>
+    <row r="1" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="B3" s="30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="34">
         <v>5</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="35">
         <f>J3*5</f>
         <v>25</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="18">
+      <c r="L3" s="35">
+        <f>J3*25</f>
+        <v>125</v>
+      </c>
+      <c r="M3" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="37">
         <v>0.1</v>
       </c>
-      <c r="N3" s="16">
-        <f>M3*J3</f>
+      <c r="O3" s="38">
+        <f>N3*J3</f>
         <v>0.5</v>
       </c>
-      <c r="O3" s="18">
+      <c r="P3" s="37">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="P3" s="16">
-        <f>O3*K3</f>
+      <c r="Q3" s="38">
+        <f>P3*K3</f>
         <v>1.4000000000000001</v>
       </c>
-      <c r="Q3" s="9"/>
+      <c r="R3" s="38">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="S3" s="38">
+        <f>R3*L3</f>
+        <v>3.1</v>
+      </c>
+      <c r="T3" s="47"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="10">
+      <c r="H4" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="42">
         <v>2</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="41">
         <f t="shared" ref="K4:K6" si="0">J4*5</f>
         <v>10</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="18">
+      <c r="L4" s="41">
+        <f t="shared" ref="L4:L6" si="1">J4*25</f>
+        <v>50</v>
+      </c>
+      <c r="M4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" s="44">
         <v>0.1</v>
       </c>
-      <c r="N4" s="16">
-        <f t="shared" ref="N4:N6" si="1">M4*J4</f>
+      <c r="O4" s="45">
+        <f t="shared" ref="O4:O6" si="2">N4*J4</f>
         <v>0.2</v>
       </c>
-      <c r="O4" s="18">
+      <c r="P4" s="44">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="P4" s="16">
-        <f t="shared" ref="P4:P6" si="2">O4*K4</f>
+      <c r="Q4" s="45">
+        <f t="shared" ref="Q4:Q6" si="3">P4*K4</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="R4" s="45">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S4" s="45">
+        <f t="shared" ref="S4:S5" si="4">R4*L4</f>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="T4" s="46"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <f t="shared" ref="A5:A6" si="3">A4+1</f>
+    <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A6" si="5">A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="10">
+      <c r="H5" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="16">
         <v>1</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="18">
+      <c r="L5" s="17">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="19">
         <v>3.23</v>
       </c>
-      <c r="N5" s="16">
-        <f t="shared" si="1"/>
+      <c r="O5" s="20">
+        <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="O5" s="18">
+      <c r="P5" s="19">
         <v>3.23</v>
       </c>
-      <c r="P5" s="16">
-        <f t="shared" si="2"/>
+      <c r="Q5" s="20">
+        <f t="shared" si="3"/>
         <v>16.149999999999999</v>
       </c>
-      <c r="Q5" s="9" t="s">
-        <v>42</v>
+      <c r="R5" s="20">
+        <v>2.8380000000000001</v>
+      </c>
+      <c r="S5" s="20">
+        <f t="shared" si="4"/>
+        <v>70.95</v>
+      </c>
+      <c r="T5" s="21" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <f t="shared" si="3"/>
+    <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="48">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="14">
+      <c r="G6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="24"/>
+      <c r="I6" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="25">
         <v>1</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="17">
+      <c r="L6" s="26">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="17">
+        <v>25</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="15" t="s">
-        <v>43</v>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="29" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J7" s="26" t="s">
+    <row r="7" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="Q7" s="3">
+        <f>SUM(Q3:Q6)</f>
+        <v>17.829999999999998</v>
+      </c>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="J8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="P7" s="20">
-        <f>SUM(P3:P6)</f>
-        <v>17.829999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J8" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="20">
-        <f>SUM(N3:N6)</f>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="3">
+        <f>SUM(O3:O6)</f>
         <v>3.9299999999999997</v>
       </c>
-      <c r="P8" s="20">
-        <f>P7/5</f>
+      <c r="Q8" s="3">
+        <f>Q7/5</f>
         <v>3.5659999999999998</v>
       </c>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:T1"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J7:N7"/>
+    <mergeCell ref="J8:N8"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:K6">
+  <conditionalFormatting sqref="J3:L6">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1147,7 +1416,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:P8">
+  <conditionalFormatting sqref="O8:S8">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -1161,7 +1430,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N6">
+  <conditionalFormatting sqref="O3:O6">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -1175,7 +1444,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P6">
+  <conditionalFormatting sqref="Q3:S6">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1190,9 +1459,9 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1"/>
-    <hyperlink ref="L4" r:id="rId2"/>
-    <hyperlink ref="L5" r:id="rId3"/>
+    <hyperlink ref="M3" r:id="rId1"/>
+    <hyperlink ref="M4" r:id="rId2"/>
+    <hyperlink ref="M5" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -1210,7 +1479,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N8:P8</xm:sqref>
+          <xm:sqref>O8:S8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9247D164-2B67-46B9-A071-A237687D6A54}">
@@ -1223,7 +1492,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N6</xm:sqref>
+          <xm:sqref>O3:O6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{70AA7481-CFEB-4BA0-AFB1-AC7B4702AFE5}">
@@ -1236,7 +1505,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P6</xm:sqref>
+          <xm:sqref>Q3:S6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
